--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92563654557</v>
+        <v>46157.93080826678</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93080826678</v>
+        <v>46157.9316011882</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9316011882</v>
+        <v>46157.93395461747</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93395461747</v>
+        <v>46157.93712390508</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93712390508</v>
+        <v>46158.28212200638</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212200638</v>
+        <v>46158.29673311332</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29673311332</v>
+        <v>46158.29808846812</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808846812</v>
+        <v>46158.33383001359</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383001359</v>
+        <v>46158.36850933821</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/17. ООО Клиентская база/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36850933821</v>
+        <v>46158.37283192199</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
